--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261021.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261021.xlsx
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>14,094,000</t>
+          <t>39,840,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>39,840,000</t>
+          <t>14,094,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>10,471,000</t>
+          <t>4,101,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>4,101,000</t>
+          <t>10,471,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,388,000</t>
+          <t>43,767,500</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>43,767,500</t>
+          <t>2,388,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>17,681,000</t>
+          <t>50,331,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>50,331,000</t>
+          <t>17,681,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
